--- a/main/ig/StructureDefinition-fr-lm-medication-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-medication-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-medication-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-medication-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-medication-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-medication-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-medication-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-medication-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-medication-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-medication-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-medication-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-medication-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-medication-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-medication-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-medication-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-medication-dispense.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="168">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -429,6 +429,9 @@
   </si>
   <si>
     <t>Statut</t>
+  </si>
+  <si>
+    <t>required</t>
   </si>
   <si>
     <t>Valeur issue du JDV_CompletudeDispensation_CISIS (1.2.250.1.213.1.1.5.765)</t>
@@ -2547,13 +2550,13 @@
         <v>73</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2571,7 +2574,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -2588,10 +2591,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2617,10 +2620,10 @@
         <v>132</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2671,7 +2674,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2688,10 +2691,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2717,10 +2720,10 @@
         <v>132</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2771,7 +2774,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2788,10 +2791,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2814,13 +2817,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2871,7 +2874,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -2888,10 +2891,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2914,13 +2917,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2971,7 +2974,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -2988,10 +2991,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3014,13 +3017,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3071,7 +3074,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3088,10 +3091,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3114,13 +3117,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3171,7 +3174,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -3188,10 +3191,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3217,10 +3220,10 @@
         <v>128</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3271,7 +3274,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3288,10 +3291,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3314,13 +3317,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3371,7 +3374,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -3388,10 +3391,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3414,13 +3417,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3471,7 +3474,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3488,10 +3491,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3514,13 +3517,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3571,7 +3574,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
